--- a/artfynd/A 54233-2023 artfynd.xlsx
+++ b/artfynd/A 54233-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,6 +1009,120 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114696385</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57381</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 948, Hjulby, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>588440</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6425714</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54233-2023 artfynd.xlsx
+++ b/artfynd/A 54233-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54233-2023 artfynd.xlsx
+++ b/artfynd/A 54233-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113232075</v>
       </c>
       <c r="B2" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,51 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113232054</v>
+        <v>113232027</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588481</v>
+        <v>588504</v>
       </c>
       <c r="R3" t="n">
-        <v>6425683</v>
+        <v>6425652</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113232027</v>
+        <v>114696385</v>
       </c>
       <c r="B4" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +897,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -935,26 +919,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 54233, Hjulby, Sm</t>
+          <t>A 948, Hjulby, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588504</v>
+        <v>588439</v>
       </c>
       <c r="R4" t="n">
-        <v>6425652</v>
+        <v>6425714</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,7 +977,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,65 +995,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114696385</v>
+        <v>113232054</v>
       </c>
       <c r="B5" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 948, Hjulby, Sm</t>
+          <t>A 54233, Hjulby, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588439</v>
+        <v>588481</v>
       </c>
       <c r="R5" t="n">
-        <v>6425714</v>
+        <v>6425683</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,12 +1072,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,6 +1086,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
